--- a/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27295020856158</v>
+        <v>1.284063592573654</v>
       </c>
       <c r="C3" t="n">
-        <v>4.677632057471402</v>
+        <v>4.746040237503319</v>
       </c>
       <c r="D3" t="n">
-        <v>6.036742183655671</v>
+        <v>6.01788281025709</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98732444968865</v>
+        <v>12.04798664033406</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.428324953797095</v>
+        <v>1.457393923876714</v>
       </c>
       <c r="C4" t="n">
-        <v>5.265947235745382</v>
+        <v>5.483565905795969</v>
       </c>
       <c r="D4" t="n">
-        <v>6.232296686484277</v>
+        <v>6.301371231788004</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92656887602675</v>
+        <v>13.24233106146069</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.641518485379247</v>
+        <v>1.678390166325129</v>
       </c>
       <c r="C5" t="n">
-        <v>6.049288149271479</v>
+        <v>6.45491073534409</v>
       </c>
       <c r="D5" t="n">
-        <v>6.457856721793105</v>
+        <v>6.539807788112267</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14866335644383</v>
+        <v>14.67310868978149</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.873508673603555</v>
+        <v>1.921877353229606</v>
       </c>
       <c r="C6" t="n">
-        <v>6.993953575903197</v>
+        <v>7.593063127725403</v>
       </c>
       <c r="D6" t="n">
-        <v>6.66204426553799</v>
+        <v>6.825617651840525</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52950651504474</v>
+        <v>16.34055813279553</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.13223546168727</v>
+        <v>2.186841303239238</v>
       </c>
       <c r="C7" t="n">
-        <v>8.112166195514163</v>
+        <v>8.88249583152465</v>
       </c>
       <c r="D7" t="n">
-        <v>6.965999738889521</v>
+        <v>7.203749925174225</v>
       </c>
       <c r="E7" t="n">
-        <v>17.21040139609095</v>
+        <v>18.27308705993811</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.342877425217855</v>
+        <v>1.351832538582765</v>
       </c>
       <c r="C8" t="n">
-        <v>5.720507469990973</v>
+        <v>6.398483407173845</v>
       </c>
       <c r="D8" t="n">
-        <v>5.135302398897541</v>
+        <v>5.461255892492646</v>
       </c>
       <c r="E8" t="n">
-        <v>12.19868729410637</v>
+        <v>13.21157183824926</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.695878577399776</v>
+        <v>1.681618939557296</v>
       </c>
       <c r="C9" t="n">
-        <v>7.048483651945669</v>
+        <v>7.957713696021022</v>
       </c>
       <c r="D9" t="n">
-        <v>5.48356976872974</v>
+        <v>5.912410850646958</v>
       </c>
       <c r="E9" t="n">
-        <v>14.22793199807519</v>
+        <v>15.55174348622528</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.08241333363908</v>
+        <v>2.022228420592577</v>
       </c>
       <c r="C10" t="n">
-        <v>8.588038362487634</v>
+        <v>9.699199881284498</v>
       </c>
       <c r="D10" t="n">
-        <v>5.819579697240054</v>
+        <v>6.455075178800796</v>
       </c>
       <c r="E10" t="n">
-        <v>16.49003139336677</v>
+        <v>18.17650348067787</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.471577513622344</v>
+        <v>2.355390409867472</v>
       </c>
       <c r="C11" t="n">
-        <v>10.23561979839755</v>
+        <v>11.54981175255404</v>
       </c>
       <c r="D11" t="n">
-        <v>6.208295808049511</v>
+        <v>6.871488754265054</v>
       </c>
       <c r="E11" t="n">
-        <v>18.91549312006941</v>
+        <v>20.77669091668657</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.854789411920517</v>
+        <v>2.665205727838799</v>
       </c>
       <c r="C12" t="n">
-        <v>12.02506138129795</v>
+        <v>13.47704699172827</v>
       </c>
       <c r="D12" t="n">
-        <v>6.690657427950004</v>
+        <v>7.34316681188703</v>
       </c>
       <c r="E12" t="n">
-        <v>21.57050822116847</v>
+        <v>23.4854195314541</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.214971523667683</v>
+        <v>2.935156489680663</v>
       </c>
       <c r="C13" t="n">
-        <v>13.8070266832053</v>
+        <v>15.37535033184334</v>
       </c>
       <c r="D13" t="n">
-        <v>7.072160840548597</v>
+        <v>7.730498960253173</v>
       </c>
       <c r="E13" t="n">
-        <v>24.09415904742158</v>
+        <v>26.04100578177718</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.844389777014398</v>
+        <v>1.677355222613846</v>
       </c>
       <c r="C14" t="n">
-        <v>9.705106200240014</v>
+        <v>10.72674231371037</v>
       </c>
       <c r="D14" t="n">
-        <v>5.41887426331478</v>
+        <v>5.908844907550277</v>
       </c>
       <c r="E14" t="n">
-        <v>16.96837024056919</v>
+        <v>18.31294244387449</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.88839170911874</v>
+        <v>1.685012854706971</v>
       </c>
       <c r="C15" t="n">
-        <v>10.53469282780561</v>
+        <v>11.58563411024774</v>
       </c>
       <c r="D15" t="n">
-        <v>5.366900539851954</v>
+        <v>5.877566425692975</v>
       </c>
       <c r="E15" t="n">
-        <v>17.78998507677631</v>
+        <v>19.14821339064768</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.197887672882547</v>
+        <v>1.917274726577681</v>
       </c>
       <c r="C16" t="n">
-        <v>12.52656074495196</v>
+        <v>13.59097160589636</v>
       </c>
       <c r="D16" t="n">
-        <v>5.713428027019949</v>
+        <v>6.332145065190375</v>
       </c>
       <c r="E16" t="n">
-        <v>20.43787644485446</v>
+        <v>21.84039139766441</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.764593323613217</v>
+        <v>1.512333251006999</v>
       </c>
       <c r="C17" t="n">
-        <v>11.57314627944972</v>
+        <v>12.33192926258504</v>
       </c>
       <c r="D17" t="n">
-        <v>5.241011031736385</v>
+        <v>5.845178568929872</v>
       </c>
       <c r="E17" t="n">
-        <v>18.57875063479932</v>
+        <v>19.68944108252191</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.012484618935537</v>
+        <v>1.701408041367893</v>
       </c>
       <c r="C18" t="n">
-        <v>13.60240896665083</v>
+        <v>14.27990323987451</v>
       </c>
       <c r="D18" t="n">
-        <v>5.60786069638229</v>
+        <v>6.19350265439664</v>
       </c>
       <c r="E18" t="n">
-        <v>21.22275428196866</v>
+        <v>22.17481393563904</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.010580028389298</v>
+        <v>1.686210586906152</v>
       </c>
       <c r="C19" t="n">
-        <v>14.61415888073943</v>
+        <v>15.12998875950478</v>
       </c>
       <c r="D19" t="n">
-        <v>5.648131987210495</v>
+        <v>6.251366864084948</v>
       </c>
       <c r="E19" t="n">
-        <v>22.27287089633922</v>
+        <v>23.06756621049588</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.222725889799991</v>
+        <v>1.859675588769521</v>
       </c>
       <c r="C20" t="n">
-        <v>16.79556300966767</v>
+        <v>17.16601568838816</v>
       </c>
       <c r="D20" t="n">
-        <v>6.034371169015275</v>
+        <v>6.669434306461409</v>
       </c>
       <c r="E20" t="n">
-        <v>25.05266006848293</v>
+        <v>25.69512558361909</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.311958544570225</v>
+        <v>1.098821117978243</v>
       </c>
       <c r="C21" t="n">
-        <v>12.35473526175469</v>
+        <v>12.4214548357353</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020039258464513</v>
+        <v>5.574294742374091</v>
       </c>
       <c r="E21" t="n">
-        <v>18.68673306478943</v>
+        <v>19.09457069608763</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.284063592573654</v>
+        <v>1.255769623737261</v>
       </c>
       <c r="C3" t="n">
-        <v>4.746040237503319</v>
+        <v>4.592897413117859</v>
       </c>
       <c r="D3" t="n">
-        <v>6.01788281025709</v>
+        <v>6.053657696599844</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04798664033406</v>
+        <v>11.90232473345496</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.457393923876714</v>
+        <v>1.393998032838451</v>
       </c>
       <c r="C4" t="n">
-        <v>5.483565905795969</v>
+        <v>5.01023919608656</v>
       </c>
       <c r="D4" t="n">
-        <v>6.301371231788004</v>
+        <v>6.25570327101657</v>
       </c>
       <c r="E4" t="n">
-        <v>13.24233106146069</v>
+        <v>12.65994049994158</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.678390166325129</v>
+        <v>1.591114477183294</v>
       </c>
       <c r="C5" t="n">
-        <v>6.45491073534409</v>
+        <v>5.519472668730558</v>
       </c>
       <c r="D5" t="n">
-        <v>6.539807788112267</v>
+        <v>6.615333476346593</v>
       </c>
       <c r="E5" t="n">
-        <v>14.67310868978149</v>
+        <v>13.72592062226044</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.921877353229606</v>
+        <v>1.822997031652901</v>
       </c>
       <c r="C6" t="n">
-        <v>7.593063127725403</v>
+        <v>6.112119818344161</v>
       </c>
       <c r="D6" t="n">
-        <v>6.825617651840525</v>
+        <v>7.066640453004543</v>
       </c>
       <c r="E6" t="n">
-        <v>16.34055813279553</v>
+        <v>15.00175730300161</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.186841303239238</v>
+        <v>2.076756759993622</v>
       </c>
       <c r="C7" t="n">
-        <v>8.88249583152465</v>
+        <v>6.773087600529223</v>
       </c>
       <c r="D7" t="n">
-        <v>7.203749925174225</v>
+        <v>7.548885139843491</v>
       </c>
       <c r="E7" t="n">
-        <v>18.27308705993811</v>
+        <v>16.39872950036634</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.351832538582765</v>
+        <v>1.297649198762392</v>
       </c>
       <c r="C8" t="n">
-        <v>6.398483407173845</v>
+        <v>4.348959617182199</v>
       </c>
       <c r="D8" t="n">
-        <v>5.461255892492646</v>
+        <v>5.945172974397472</v>
       </c>
       <c r="E8" t="n">
-        <v>13.21157183824926</v>
+        <v>11.59178179034206</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.681618939557296</v>
+        <v>1.634864607576549</v>
       </c>
       <c r="C9" t="n">
-        <v>7.957713696021022</v>
+        <v>5.198459664814838</v>
       </c>
       <c r="D9" t="n">
-        <v>5.912410850646958</v>
+        <v>6.647758041738461</v>
       </c>
       <c r="E9" t="n">
-        <v>15.55174348622528</v>
+        <v>13.48108231412985</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.022228420592577</v>
+        <v>1.985920044406339</v>
       </c>
       <c r="C10" t="n">
-        <v>9.699199881284498</v>
+        <v>6.194144942165722</v>
       </c>
       <c r="D10" t="n">
-        <v>6.455075178800796</v>
+        <v>7.313629215904759</v>
       </c>
       <c r="E10" t="n">
-        <v>18.17650348067787</v>
+        <v>15.49369420247682</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.355390409867472</v>
+        <v>2.35136472200921</v>
       </c>
       <c r="C11" t="n">
-        <v>11.54981175255404</v>
+        <v>7.346344912584533</v>
       </c>
       <c r="D11" t="n">
-        <v>6.871488754265054</v>
+        <v>8.06228689182929</v>
       </c>
       <c r="E11" t="n">
-        <v>20.77669091668657</v>
+        <v>17.75999652642303</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.665205727838799</v>
+        <v>2.742321495742691</v>
       </c>
       <c r="C12" t="n">
-        <v>13.47704699172827</v>
+        <v>8.588464396460237</v>
       </c>
       <c r="D12" t="n">
-        <v>7.34316681188703</v>
+        <v>8.784025274106947</v>
       </c>
       <c r="E12" t="n">
-        <v>23.4854195314541</v>
+        <v>20.11481116630987</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.935156489680663</v>
+        <v>3.138355002198162</v>
       </c>
       <c r="C13" t="n">
-        <v>15.37535033184334</v>
+        <v>9.882156244934796</v>
       </c>
       <c r="D13" t="n">
-        <v>7.730498960253173</v>
+        <v>9.43995255389841</v>
       </c>
       <c r="E13" t="n">
-        <v>26.04100578177718</v>
+        <v>22.46046380103137</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.677355222613846</v>
+        <v>1.832412455022587</v>
       </c>
       <c r="C14" t="n">
-        <v>10.72674231371037</v>
+        <v>7.017002446195908</v>
       </c>
       <c r="D14" t="n">
-        <v>5.908844907550277</v>
+        <v>7.230454032053248</v>
       </c>
       <c r="E14" t="n">
-        <v>18.31294244387449</v>
+        <v>16.07986893327174</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.685012854706971</v>
+        <v>1.907771408800572</v>
       </c>
       <c r="C15" t="n">
-        <v>11.58563411024774</v>
+        <v>7.527678149513972</v>
       </c>
       <c r="D15" t="n">
-        <v>5.877566425692975</v>
+        <v>7.386659909275958</v>
       </c>
       <c r="E15" t="n">
-        <v>19.14821339064768</v>
+        <v>16.8221094675905</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.917274726577681</v>
+        <v>2.243136424571282</v>
       </c>
       <c r="C16" t="n">
-        <v>13.59097160589636</v>
+        <v>8.904255327977722</v>
       </c>
       <c r="D16" t="n">
-        <v>6.332145065190375</v>
+        <v>8.051764526472045</v>
       </c>
       <c r="E16" t="n">
-        <v>21.84039139766441</v>
+        <v>19.19915627902105</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.512333251006999</v>
+        <v>1.820278053398096</v>
       </c>
       <c r="C17" t="n">
-        <v>12.33192926258504</v>
+        <v>8.295198687217084</v>
       </c>
       <c r="D17" t="n">
-        <v>5.845178568929872</v>
+        <v>7.612815310426254</v>
       </c>
       <c r="E17" t="n">
-        <v>19.68944108252191</v>
+        <v>17.72829205104144</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.701408041367893</v>
+        <v>2.100233228741117</v>
       </c>
       <c r="C18" t="n">
-        <v>14.27990323987451</v>
+        <v>9.690321079814057</v>
       </c>
       <c r="D18" t="n">
-        <v>6.19350265439664</v>
+        <v>8.231591253458934</v>
       </c>
       <c r="E18" t="n">
-        <v>22.17481393563904</v>
+        <v>20.02214556201411</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.686210586906152</v>
+        <v>2.129067158814846</v>
       </c>
       <c r="C19" t="n">
-        <v>15.12998875950478</v>
+        <v>10.38619367006124</v>
       </c>
       <c r="D19" t="n">
-        <v>6.251366864084948</v>
+        <v>8.464520713768533</v>
       </c>
       <c r="E19" t="n">
-        <v>23.06756621049588</v>
+        <v>20.97978154264462</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.859675588769521</v>
+        <v>2.385715643659047</v>
       </c>
       <c r="C20" t="n">
-        <v>17.16601568838816</v>
+        <v>11.9921660170993</v>
       </c>
       <c r="D20" t="n">
-        <v>6.669434306461409</v>
+        <v>9.145313659278482</v>
       </c>
       <c r="E20" t="n">
-        <v>25.69512558361909</v>
+        <v>23.52319532003683</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.098821117978243</v>
+        <v>1.426813208490059</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4214548357353</v>
+        <v>8.899444764226912</v>
       </c>
       <c r="D21" t="n">
-        <v>5.574294742374091</v>
+        <v>7.717548155515304</v>
       </c>
       <c r="E21" t="n">
-        <v>19.09457069608763</v>
+        <v>18.04380612823228</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_86_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255769623737261</v>
+        <v>2.575123750122914</v>
       </c>
       <c r="C3" t="n">
-        <v>4.592897413117859</v>
+        <v>7.837240004973581</v>
       </c>
       <c r="D3" t="n">
-        <v>6.053657696599844</v>
+        <v>8.165605795313928</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90232473345496</v>
+        <v>18.57796955041042</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393998032838451</v>
+        <v>1.035627242300234</v>
       </c>
       <c r="C4" t="n">
-        <v>5.01023919608656</v>
+        <v>4.803932110759428</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25570327101657</v>
+        <v>5.788776590425381</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65994049994158</v>
+        <v>11.62833594348504</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.591114477183294</v>
+        <v>1.097169823584562</v>
       </c>
       <c r="C5" t="n">
-        <v>5.519472668730558</v>
+        <v>5.808156660387229</v>
       </c>
       <c r="D5" t="n">
-        <v>6.615333476346593</v>
+        <v>6.140945426915344</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72592062226044</v>
+        <v>13.04627191088714</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.822997031652901</v>
+        <v>1.1745511404844</v>
       </c>
       <c r="C6" t="n">
-        <v>6.112119818344161</v>
+        <v>7.07313030173149</v>
       </c>
       <c r="D6" t="n">
-        <v>7.066640453004543</v>
+        <v>6.50234542337055</v>
       </c>
       <c r="E6" t="n">
-        <v>15.00175730300161</v>
+        <v>14.75002686558644</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.076756759993622</v>
+        <v>1.251387864202427</v>
       </c>
       <c r="C7" t="n">
-        <v>6.773087600529223</v>
+        <v>8.538243361820324</v>
       </c>
       <c r="D7" t="n">
-        <v>7.548885139843491</v>
+        <v>6.865804662760328</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39872950036634</v>
+        <v>16.65543588878308</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.297649198762392</v>
+        <v>1.324656740096774</v>
       </c>
       <c r="C8" t="n">
-        <v>4.348959617182199</v>
+        <v>10.17336795443431</v>
       </c>
       <c r="D8" t="n">
-        <v>5.945172974397472</v>
+        <v>7.281459329085791</v>
       </c>
       <c r="E8" t="n">
-        <v>11.59178179034206</v>
+        <v>18.77948402361688</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.634864607576549</v>
+        <v>1.392778674410067</v>
       </c>
       <c r="C9" t="n">
-        <v>5.198459664814838</v>
+        <v>11.88928202739731</v>
       </c>
       <c r="D9" t="n">
-        <v>6.647758041738461</v>
+        <v>7.682433801277678</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48108231412985</v>
+        <v>20.96449450308505</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.985920044406339</v>
+        <v>0.8935573079743195</v>
       </c>
       <c r="C10" t="n">
-        <v>6.194144942165722</v>
+        <v>8.419949367995725</v>
       </c>
       <c r="D10" t="n">
-        <v>7.313629215904759</v>
+        <v>6.035951782819112</v>
       </c>
       <c r="E10" t="n">
-        <v>15.49369420247682</v>
+        <v>15.34945845878916</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.35136472200921</v>
+        <v>0.8063192069749477</v>
       </c>
       <c r="C11" t="n">
-        <v>7.346344912584533</v>
+        <v>9.207281574370542</v>
       </c>
       <c r="D11" t="n">
-        <v>8.06228689182929</v>
+        <v>5.885332050033567</v>
       </c>
       <c r="E11" t="n">
-        <v>17.75999652642303</v>
+        <v>15.89893283137906</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.742321495742691</v>
+        <v>0.8380100228680348</v>
       </c>
       <c r="C12" t="n">
-        <v>8.588464396460237</v>
+        <v>10.99526012829892</v>
       </c>
       <c r="D12" t="n">
-        <v>8.784025274106947</v>
+        <v>6.218124886819151</v>
       </c>
       <c r="E12" t="n">
-        <v>20.11481116630987</v>
+        <v>18.0513950379861</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.138355002198162</v>
+        <v>0.6481301993896593</v>
       </c>
       <c r="C13" t="n">
-        <v>9.882156244934796</v>
+        <v>10.47177261744043</v>
       </c>
       <c r="D13" t="n">
-        <v>9.43995255389841</v>
+        <v>5.640336910438775</v>
       </c>
       <c r="E13" t="n">
-        <v>22.46046380103137</v>
+        <v>16.76023972726887</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.832412455022587</v>
+        <v>0.6783778461575035</v>
       </c>
       <c r="C14" t="n">
-        <v>7.017002446195908</v>
+        <v>12.32555771998447</v>
       </c>
       <c r="D14" t="n">
-        <v>7.230454032053248</v>
+        <v>6.000147444045231</v>
       </c>
       <c r="E14" t="n">
-        <v>16.07986893327174</v>
+        <v>19.00408301018721</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.907771408800572</v>
+        <v>0.6388035961993146</v>
       </c>
       <c r="C15" t="n">
-        <v>7.527678149513972</v>
+        <v>13.31934165108535</v>
       </c>
       <c r="D15" t="n">
-        <v>7.386659909275958</v>
+        <v>6.022266219821912</v>
       </c>
       <c r="E15" t="n">
-        <v>16.8221094675905</v>
+        <v>19.98041146710658</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.243136424571282</v>
+        <v>0.6854366121510381</v>
       </c>
       <c r="C16" t="n">
-        <v>8.904255327977722</v>
+        <v>15.49377537131344</v>
       </c>
       <c r="D16" t="n">
-        <v>8.051764526472045</v>
+        <v>6.382606897188662</v>
       </c>
       <c r="E16" t="n">
-        <v>19.19915627902105</v>
+        <v>22.56181888065314</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.820278053398096</v>
+        <v>0.4099483888623406</v>
       </c>
       <c r="C17" t="n">
-        <v>8.295198687217084</v>
+        <v>11.48773422918025</v>
       </c>
       <c r="D17" t="n">
-        <v>7.612815310426254</v>
+        <v>5.292542968732301</v>
       </c>
       <c r="E17" t="n">
-        <v>17.72829205104144</v>
+        <v>17.19022558677489</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.100233228741117</v>
+        <v>0.3129615331597982</v>
       </c>
       <c r="C18" t="n">
-        <v>9.690321079814057</v>
+        <v>10.40596606882477</v>
       </c>
       <c r="D18" t="n">
-        <v>8.231591253458934</v>
+        <v>4.803053380871883</v>
       </c>
       <c r="E18" t="n">
-        <v>20.02214556201411</v>
+        <v>15.52198098285645</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.129067158814846</v>
+        <v>0.3602130501651973</v>
       </c>
       <c r="C19" t="n">
-        <v>10.38619367006124</v>
+        <v>12.82940045928098</v>
       </c>
       <c r="D19" t="n">
-        <v>8.464520713768533</v>
+        <v>5.270021676396878</v>
       </c>
       <c r="E19" t="n">
-        <v>20.97978154264462</v>
+        <v>18.45963518584305</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.385715643659047</v>
+        <v>0.4018097003941346</v>
       </c>
       <c r="C20" t="n">
-        <v>11.9921660170993</v>
+        <v>15.28017652330046</v>
       </c>
       <c r="D20" t="n">
-        <v>9.145313659278482</v>
+        <v>5.695952917884357</v>
       </c>
       <c r="E20" t="n">
-        <v>23.52319532003683</v>
+        <v>21.37793914157895</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.426813208490059</v>
+        <v>0.4359352505937537</v>
       </c>
       <c r="C21" t="n">
-        <v>8.899444764226912</v>
+        <v>17.78103153771357</v>
       </c>
       <c r="D21" t="n">
-        <v>7.717548155515304</v>
+        <v>6.056539032177168</v>
       </c>
       <c r="E21" t="n">
-        <v>18.04380612823228</v>
+        <v>24.27350582048449</v>
       </c>
     </row>
   </sheetData>
